--- a/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1184,7 +1184,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evaluation-douleur-cisis|20260716085853</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evaluation-douleur-cisis|20260916095456</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
